--- a/exports/HYUNDAI_full_report.xlsx
+++ b/exports/HYUNDAI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>14.96</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1820</v>
+        <v>1727.9</v>
       </c>
       <c r="I2" t="n">
         <v>1728.096238920276</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.06</v>
+        <v>-2.16</v>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>2.94</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>1.81</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>4.12</v>
       </c>
       <c r="O2" t="n">
         <v>-2.1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>9.25</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1847.95</v>
+        <v>1854.9</v>
       </c>
       <c r="I3" t="n">
         <v>1854.270004824821</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.95</v>
+        <v>-7.35</v>
       </c>
       <c r="L3" t="n">
-        <v>7.59</v>
+        <v>7.65</v>
       </c>
       <c r="M3" t="n">
         <v>0.28</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>6.14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1825</v>
+        <v>1785.65</v>
       </c>
       <c r="I4" t="n">
         <v>1818.376176489882</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.61</v>
+        <v>-3.73</v>
       </c>
       <c r="L4" t="n">
-        <v>1.94</v>
+        <v>4.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1.84</v>
+        <v>3.07</v>
       </c>
       <c r="N4" t="n">
         <v>1.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>4.33</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1684.1</v>
+        <v>1721.6</v>
       </c>
       <c r="I5" t="n">
         <v>1715.748880000922</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K5" t="n">
-        <v>5.69</v>
+        <v>3.59</v>
       </c>
       <c r="L5" t="n">
         <v>4.22</v>
@@ -726,7 +785,7 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.76</v>
+        <v>3.97</v>
       </c>
       <c r="O5" t="n">
         <v>-1.42</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1828.9</v>
+        <v>1702.7</v>
       </c>
       <c r="I6" t="n">
         <v>1769.67139230033</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>6.23</v>
+        <v>-1.1</v>
       </c>
       <c r="L6" t="n">
         <v>3.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.46</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.53</v>
+        <v>5.85</v>
       </c>
       <c r="O6" t="n">
         <v>3.97</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1629</v>
+        <v>1683.9</v>
       </c>
       <c r="I7" t="n">
         <v>1670.490848444957</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>1.1</v>
       </c>
       <c r="L7" t="n">
         <v>6.5</v>
@@ -840,7 +923,7 @@
         <v>2.21</v>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>3.96</v>
       </c>
       <c r="O7" t="n">
         <v>-5.85</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.67</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1703.25</v>
+        <v>1651</v>
       </c>
       <c r="I8" t="n">
         <v>1651.148810160366</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>1.15</v>
+        <v>-1.95</v>
       </c>
       <c r="L8" t="n">
         <v>3.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.18</v>
+        <v>2.27</v>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>3.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1639.5</v>
+        <v>1698.8</v>
       </c>
       <c r="I9" t="n">
         <v>1691.607961434074</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>-2.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>2.96</v>
       </c>
       <c r="M9" t="n">
         <v>2.08</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2108.9</v>
+        <v>2086.9</v>
       </c>
       <c r="I10" t="n">
         <v>2088.883937032746</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>24.14</v>
+        <v>22.85</v>
       </c>
       <c r="L10" t="n">
         <v>3.71</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.59</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2150</v>
+        <v>2173.4</v>
       </c>
       <c r="I11" t="n">
         <v>2150.43039030006</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.02</v>
+        <v>-4.14</v>
       </c>
       <c r="L11" t="n">
-        <v>3.81</v>
+        <v>5.42</v>
       </c>
       <c r="M11" t="n">
         <v>0.7</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.33</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45891.38541666666</v>
+        <v>45891.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>2409.2</v>
+        <v>2365</v>
       </c>
       <c r="I12" t="n">
         <v>2369.175628605869</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>10.85</v>
+        <v>8.82</v>
       </c>
       <c r="L12" t="n">
         <v>3.37</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.82</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45916.38541666666</v>
+        <v>45916.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2581.7</v>
+        <v>2608.5</v>
       </c>
       <c r="I13" t="n">
         <v>2597.318873208068</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.16</v>
+        <v>-10.3</v>
       </c>
       <c r="L13" t="n">
-        <v>10.79</v>
+        <v>11.16</v>
       </c>
       <c r="M13" t="n">
         <v>2.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2678.4</v>
+        <v>2635</v>
       </c>
       <c r="I14" t="n">
         <v>2638.546004962032</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="L14" t="n">
         <v>1.84</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.92</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45960.38541666666</v>
+        <v>45960.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2358.2</v>
+        <v>2421.1</v>
       </c>
       <c r="I15" t="n">
         <v>2394.143604504621</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>10.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>2.69</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2333.8</v>
+        <v>2309</v>
       </c>
       <c r="I16" t="n">
         <v>2313.585669590869</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.61</v>
+        <v>-4.63</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>6.03</v>
       </c>
       <c r="M16" t="n">
         <v>0.66</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.21</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2308.9</v>
+        <v>2342.2</v>
       </c>
       <c r="I17" t="n">
         <v>2341.141427044451</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-1.44</v>
       </c>
       <c r="L17" t="n">
         <v>4.81</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.53</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2349</v>
+        <v>2264.5</v>
       </c>
       <c r="I18" t="n">
         <v>2267.807633093063</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.29</v>
+        <v>-3.32</v>
       </c>
       <c r="L18" t="n">
-        <v>2.16</v>
+        <v>3.66</v>
       </c>
       <c r="M18" t="n">
-        <v>-0</v>
+        <v>0.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>2.08</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>6.14</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2250</v>
+        <v>2271.5</v>
       </c>
       <c r="I19" t="n">
         <v>2250.058518166386</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K19" t="n">
-        <v>0.64</v>
+        <v>-0.31</v>
       </c>
       <c r="L19" t="n">
         <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
         <v>3.73</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>7.22</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2173</v>
+        <v>2131.2</v>
       </c>
       <c r="I20" t="n">
         <v>2144.770437216737</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.34</v>
+        <v>-6.18</v>
       </c>
       <c r="L20" t="n">
-        <v>5.75</v>
+        <v>7.75</v>
       </c>
       <c r="M20" t="n">
-        <v>0.48</v>
+        <v>3.13</v>
       </c>
       <c r="N20" t="n">
         <v>4.67</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.67</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46128.38541666666</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1809</v>
+        <v>1851.5</v>
       </c>
       <c r="I21" t="n">
         <v>1824.483726529951</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>15.12</v>
+        <v>13.12</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1838.9</v>
+        <v>1774.6</v>
       </c>
       <c r="I22" t="n">
         <v>1777.367736002766</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.68</v>
+        <v>-4.15</v>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>4.28</v>
       </c>
       <c r="M22" t="n">
         <v>0.32</v>
       </c>
       <c r="N22" t="n">
-        <v>1.81</v>
+        <v>3.13</v>
       </c>
       <c r="O22" t="n">
         <v>3.96</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1886.6</v>
+        <v>1905</v>
       </c>
       <c r="I23" t="n">
         <v>1899.328506760954</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.31</v>
+        <v>-7.35</v>
       </c>
       <c r="L23" t="n">
         <v>9.550000000000001</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1822</v>
+        <v>1777.8</v>
       </c>
       <c r="I24" t="n">
         <v>1782.817232115077</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.36</v>
+        <v>-6.68</v>
       </c>
       <c r="L24" t="n">
-        <v>5.28</v>
+        <v>7.29</v>
       </c>
       <c r="M24" t="n">
         <v>2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
         <v>3.92</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.46</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1887</v>
+        <v>1897.2</v>
       </c>
       <c r="I25" t="n">
         <v>1887.683582603934</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.14</v>
+        <v>-6.72</v>
       </c>
       <c r="L25" t="n">
-        <v>7.15</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>0.73</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.23</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46202.38541666666</v>
+        <v>46202.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1917</v>
+        <v>1900.9</v>
       </c>
       <c r="I26" t="n">
         <v>1915.56983691544</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>1.04</v>
+        <v>0.2</v>
       </c>
       <c r="L26" t="n">
         <v>2.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46209.38541666666</v>
+        <v>46209.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1994.2</v>
+        <v>2006.6</v>
       </c>
       <c r="I27" t="n">
         <v>2003.453814799944</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.91</v>
+        <v>-5.56</v>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
         <v>0.41</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.48</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1949.4</v>
+        <v>1915.8</v>
       </c>
       <c r="I28" t="n">
         <v>1916.675122757431</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.85</v>
+        <v>-4.53</v>
       </c>
       <c r="L28" t="n">
-        <v>3.27</v>
+        <v>5.11</v>
       </c>
       <c r="M28" t="n">
         <v>0.33</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.6</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46218.55208333334</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2004</v>
+        <v>2059.2</v>
       </c>
       <c r="I29" t="n">
         <v>2010.607954762964</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.6</v>
+        <v>-7.49</v>
       </c>
       <c r="L29" t="n">
-        <v>6.69</v>
+        <v>7.53</v>
       </c>
       <c r="M29" t="n">
         <v>1.84</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.43</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46266.38541666666</v>
+        <v>46266.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>2190</v>
+        <v>2168</v>
       </c>
       <c r="I30" t="n">
         <v>2175.741695364722</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>6.35</v>
+        <v>5.28</v>
       </c>
       <c r="L30" t="n">
         <v>6.4</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2211,6 +2582,14 @@
       <c r="Q31" t="n">
         <v>75</v>
       </c>
+      <c r="R31" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3191,7 +3570,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -3201,7 +3580,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -3211,7 +3590,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -3221,7 +3600,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3231,7 +3610,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -3241,7 +3620,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -3281,7 +3660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.18</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="15">
@@ -3291,7 +3670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.56</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="16">
@@ -3301,7 +3680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.29</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="17">
@@ -3311,7 +3690,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.14</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="18">
@@ -3321,7 +3700,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -3331,7 +3710,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.35</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="20">
@@ -3341,7 +3720,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="21">
@@ -3351,7 +3730,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.79</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="22">
@@ -3361,7 +3740,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -3381,7 +3760,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -3391,7 +3770,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="26">
@@ -3401,7 +3780,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.17</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="27">
@@ -3411,7 +3790,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.68</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="28">
@@ -3421,7 +3800,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
